--- a/inbox/Team Project Tracker .xlsx
+++ b/inbox/Team Project Tracker .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\605007126\AppData\Local\Box\Box Edit\Documents\K3nRkl24g062jOyJ52M75A==\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{3AF123D8-780B-4568-9F96-B95694DB96D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{824C3C15-CD0A-45C6-B7D4-BCE77A407D7A}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{3AF123D8-780B-4568-9F96-B95694DB96D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06C52C6E-AE4C-498B-96E7-AB20ACE3FBBC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFS Training Action Plan Tracke" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11680" uniqueCount="3223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11719" uniqueCount="3262">
   <si>
     <t>AP#</t>
   </si>
@@ -9923,6 +9923,123 @@
   </si>
   <si>
     <t>Competency Open Hours: Next schedule June 23, 30, &amp; July 20</t>
+  </si>
+  <si>
+    <t>Overseeing MyTech help desk agents - Answering escalations, monitoring ticket times, knowledge transfer/QA-ing documentation</t>
+  </si>
+  <si>
+    <t>Provide ELT Kahuna Training @HLC</t>
+  </si>
+  <si>
+    <t>Aero Alliance System Demo</t>
+  </si>
+  <si>
+    <t>Function review of Primary Roles without levels i.e. Welders per Beyzas work intake</t>
+  </si>
+  <si>
+    <t>New Course Outline Database Workflow Pilot - Teach MyTech process and handoff</t>
+  </si>
+  <si>
+    <t>Identify Workday to Kahuna Job Codes/EE attributes for alignment/migration</t>
+  </si>
+  <si>
+    <t>Indentify List of current Competency Related Learning Resources for flagging during WD migration</t>
+  </si>
+  <si>
+    <t>Establish process or administrative access for WD to add Learning Resources to Kahuna</t>
+  </si>
+  <si>
+    <t>Kahuna Technical Connect calls</t>
+  </si>
+  <si>
+    <t>OSS Winder/Machinist Kahuna End-User Training Sessions (2 scheduled for July)</t>
+  </si>
+  <si>
+    <t>ISM Shared Systems Integration Meetings</t>
+  </si>
+  <si>
+    <t>Workday Migration Meetings</t>
+  </si>
+  <si>
+    <t>OSS Integration Meetings (Katie)</t>
+  </si>
+  <si>
+    <t>NDT Competency Map build</t>
+  </si>
+  <si>
+    <t>NDT User profile creation (Manual accounts needed until WD transition)</t>
+  </si>
+  <si>
+    <t>NDT Kahuna End-User Training Sessions</t>
+  </si>
+  <si>
+    <t>Create TLT Kahuna Training Sessions/Presentation</t>
+  </si>
+  <si>
+    <t>Data Analysis on Craft population attending TLT for prep-work</t>
+  </si>
+  <si>
+    <t>Develop/Maintain Competency Sharepoint Site</t>
+  </si>
+  <si>
+    <t>Create Competency AI Prompts for consistent map implementation</t>
+  </si>
+  <si>
+    <t>RD Calls/Briefing PPTs for Kahuna map rollout</t>
+  </si>
+  <si>
+    <t>Add Lucas Rigging competency updates &amp; map list of competencies to Roles he provided</t>
+  </si>
+  <si>
+    <t>Kahuna RACI chart project with Jen - create Standard Work for any gaps</t>
+  </si>
+  <si>
+    <t>Run metrics Quarterly OFS Training Numbers</t>
+  </si>
+  <si>
+    <t>Advising on Competency Structure/system implications for new competency maps (standing program mngr. calls)</t>
+  </si>
+  <si>
+    <t>WD Learning Downstream Application Testing with Heather</t>
+  </si>
+  <si>
+    <t>Competency/Kahuna official Email Communications (completing template/emailing impacted population) per Comp Map completion</t>
+  </si>
+  <si>
+    <t>Maintain/post updates to Kahuna Teams Channel</t>
+  </si>
+  <si>
+    <t>Coordinate system purge of outdated Pending Reviews</t>
+  </si>
+  <si>
+    <t>QA/Overseeing agining assessment and non-compliant Assessors (need to establish how to address)</t>
+  </si>
+  <si>
+    <t>Review/Communication Kahuna Production Updates and system maintenance</t>
+  </si>
+  <si>
+    <t>LES Workshop ppt report out summary</t>
+  </si>
+  <si>
+    <t>Controls Map implementatino QA/oversight</t>
+  </si>
+  <si>
+    <t>Testing - New Filter Experience deployment in August Release</t>
+  </si>
+  <si>
+    <t>Update Internal Controls Catalog Course Codes in Kahuna for Jen/Mohammed</t>
+  </si>
+  <si>
+    <t>Update Crane Operation competencies for Luca</t>
+  </si>
+  <si>
+    <t>Womens Network Houston Hub communications Lead</t>
+  </si>
+  <si>
+    <t>MiniMax Project? with Greg/Tam</t>
+  </si>
+  <si>
+    <t>Competency documentation for library</t>
   </si>
   <si>
     <t>15Jun26-To be put on hold &amp; start/end dates updated to allow time to test how it went with other frames first.
@@ -72277,7 +72394,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF162A9-D4D6-49F1-B73F-2AEFC24D0DA0}">
-  <dimension ref="A1:AD50"/>
+  <dimension ref="A1:AD89"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -74953,6 +75070,201 @@
     <row r="50" spans="2:2">
       <c r="B50" t="s">
         <v>3126</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" t="s">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" t="s">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" t="s">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" t="s">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" t="s">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" t="s">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" t="s">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" t="s">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>3142</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" t="s">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" t="s">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" t="s">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" t="s">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" t="s">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" t="s">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" t="s">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" t="s">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" t="s">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" t="s">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" t="s">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" t="s">
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" t="s">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" t="s">
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" t="s">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" t="s">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" t="s">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" t="s">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" t="s">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" t="s">
+        <v>3165</v>
       </c>
     </row>
   </sheetData>
@@ -75747,7 +76059,7 @@
       </c>
       <c r="R12" s="44"/>
       <c r="S12" s="46" t="s">
-        <v>3127</v>
+        <v>3166</v>
       </c>
       <c r="T12" s="44"/>
       <c r="U12" s="44" t="s">
@@ -76279,10 +76591,10 @@
     </row>
     <row r="21" spans="1:30" ht="26.45">
       <c r="B21" s="95" t="s">
-        <v>3128</v>
+        <v>3167</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>3129</v>
+        <v>3168</v>
       </c>
       <c r="F21" t="s">
         <v>146</v>
@@ -76291,15 +76603,15 @@
         <v>44928</v>
       </c>
       <c r="N21" t="s">
-        <v>3130</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="22" spans="1:30">
       <c r="B22" s="95" t="s">
-        <v>3131</v>
+        <v>3170</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>3132</v>
+        <v>3171</v>
       </c>
       <c r="F22" t="s">
         <v>146</v>
@@ -76311,15 +76623,15 @@
         <v>46234</v>
       </c>
       <c r="N22" t="s">
-        <v>3130</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="23" spans="1:30">
       <c r="B23" s="95" t="s">
-        <v>3131</v>
+        <v>3170</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>3133</v>
+        <v>3172</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -76331,15 +76643,15 @@
         <v>46203</v>
       </c>
       <c r="N23" t="s">
-        <v>3130</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="26.45">
       <c r="B24" s="95" t="s">
-        <v>3134</v>
+        <v>3173</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>3135</v>
+        <v>3174</v>
       </c>
       <c r="F24" t="s">
         <v>146</v>
@@ -76351,15 +76663,15 @@
         <v>46234</v>
       </c>
       <c r="N24" t="s">
-        <v>3130</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="39.6">
       <c r="B25" s="95" t="s">
-        <v>3136</v>
+        <v>3175</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>3137</v>
+        <v>3176</v>
       </c>
       <c r="F25" t="s">
         <v>146</v>
@@ -76373,15 +76685,15 @@
     </row>
     <row r="26" spans="1:30">
       <c r="B26" s="95" t="s">
-        <v>3138</v>
+        <v>3177</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>3139</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="26.45">
       <c r="B27" s="95" t="s">
-        <v>3140</v>
+        <v>3179</v>
       </c>
     </row>
   </sheetData>
@@ -76643,17 +76955,17 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" s="102" t="s">
-        <v>3141</v>
+        <v>3180</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>3142</v>
+        <v>3181</v>
       </c>
       <c r="C4" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D4" s="103"/>
       <c r="E4" s="103" t="s">
-        <v>3143</v>
+        <v>3182</v>
       </c>
       <c r="F4" s="103" t="s">
         <v>57</v>
@@ -76687,17 +76999,17 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" s="102" t="s">
-        <v>3144</v>
+        <v>3183</v>
       </c>
       <c r="B5" s="102" t="s">
-        <v>3145</v>
+        <v>3184</v>
       </c>
       <c r="C5" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D5" s="103"/>
       <c r="E5" s="103" t="s">
-        <v>3146</v>
+        <v>3185</v>
       </c>
       <c r="F5" s="103" t="s">
         <v>57</v>
@@ -76732,14 +77044,14 @@
     <row r="6" spans="1:30">
       <c r="A6" s="102"/>
       <c r="B6" s="102" t="s">
-        <v>3147</v>
+        <v>3186</v>
       </c>
       <c r="C6" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D6" s="103"/>
       <c r="E6" s="103" t="s">
-        <v>3148</v>
+        <v>3187</v>
       </c>
       <c r="F6" s="103" t="s">
         <v>146</v>
@@ -76753,16 +77065,16 @@
     <row r="7" spans="1:30" ht="22.9">
       <c r="A7" s="102"/>
       <c r="B7" s="102" t="s">
-        <v>3149</v>
+        <v>3188</v>
       </c>
       <c r="C7" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D7" s="109" t="s">
-        <v>3150</v>
+        <v>3189</v>
       </c>
       <c r="E7" s="103" t="s">
-        <v>3151</v>
+        <v>3190</v>
       </c>
       <c r="F7" s="103" t="s">
         <v>146</v>
@@ -76778,14 +77090,14 @@
     <row r="8" spans="1:30" ht="22.9">
       <c r="A8" s="103"/>
       <c r="B8" s="103" t="s">
-        <v>3152</v>
+        <v>3191</v>
       </c>
       <c r="C8" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D8" s="103"/>
       <c r="E8" s="103" t="s">
-        <v>3153</v>
+        <v>3192</v>
       </c>
       <c r="F8" s="103" t="s">
         <v>57</v>
@@ -76801,14 +77113,14 @@
     <row r="9" spans="1:30" ht="22.9">
       <c r="A9" s="103"/>
       <c r="B9" s="103" t="s">
-        <v>3154</v>
+        <v>3193</v>
       </c>
       <c r="C9" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D9" s="103"/>
       <c r="E9" s="103" t="s">
-        <v>3155</v>
+        <v>3194</v>
       </c>
       <c r="F9" s="103" t="s">
         <v>57</v>
@@ -76821,22 +77133,22 @@
       </c>
       <c r="K9" s="102"/>
       <c r="N9" s="107" t="s">
-        <v>3156</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="34.15">
       <c r="A10" s="103"/>
       <c r="B10" s="103" t="s">
-        <v>3157</v>
+        <v>3196</v>
       </c>
       <c r="C10" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D10" s="103" t="s">
-        <v>3158</v>
+        <v>3197</v>
       </c>
       <c r="E10" s="103" t="s">
-        <v>3159</v>
+        <v>3198</v>
       </c>
       <c r="F10" s="103" t="s">
         <v>57</v>
@@ -76849,22 +77161,22 @@
       </c>
       <c r="K10" s="102"/>
       <c r="N10" s="107" t="s">
-        <v>3160</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="22.9">
       <c r="A11" s="103"/>
       <c r="B11" s="103" t="s">
-        <v>3161</v>
+        <v>3200</v>
       </c>
       <c r="C11" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D11" s="103" t="s">
-        <v>3158</v>
+        <v>3197</v>
       </c>
       <c r="E11" s="103" t="s">
-        <v>3162</v>
+        <v>3201</v>
       </c>
       <c r="F11" s="103" t="s">
         <v>57</v>
@@ -76877,22 +77189,22 @@
       </c>
       <c r="K11" s="102"/>
       <c r="N11" s="107" t="s">
-        <v>3160</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="22.9">
       <c r="A12" s="103"/>
       <c r="B12" s="103" t="s">
-        <v>3163</v>
+        <v>3202</v>
       </c>
       <c r="C12" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D12" s="103" t="s">
-        <v>3164</v>
+        <v>3203</v>
       </c>
       <c r="E12" s="103" t="s">
-        <v>3165</v>
+        <v>3204</v>
       </c>
       <c r="F12" s="103" t="s">
         <v>57</v>
@@ -76906,14 +77218,14 @@
     <row r="13" spans="1:30" ht="22.9">
       <c r="A13" s="103"/>
       <c r="B13" s="103" t="s">
-        <v>3166</v>
+        <v>3205</v>
       </c>
       <c r="C13" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D13" s="103"/>
       <c r="E13" s="103" t="s">
-        <v>3167</v>
+        <v>3206</v>
       </c>
       <c r="F13" s="103" t="s">
         <v>57</v>
@@ -76929,14 +77241,14 @@
     <row r="14" spans="1:30" ht="22.9">
       <c r="A14" s="103"/>
       <c r="B14" s="103" t="s">
-        <v>3168</v>
+        <v>3207</v>
       </c>
       <c r="C14" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D14" s="103"/>
       <c r="E14" s="103" t="s">
-        <v>3167</v>
+        <v>3206</v>
       </c>
       <c r="F14" s="103" t="s">
         <v>57</v>
@@ -76952,14 +77264,14 @@
     <row r="15" spans="1:30" ht="22.9">
       <c r="A15" s="103"/>
       <c r="B15" s="103" t="s">
-        <v>3169</v>
+        <v>3208</v>
       </c>
       <c r="C15" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D15" s="103"/>
       <c r="E15" s="103" t="s">
-        <v>3167</v>
+        <v>3206</v>
       </c>
       <c r="F15" s="103" t="s">
         <v>57</v>
@@ -76975,16 +77287,16 @@
     <row r="16" spans="1:30" ht="102.6">
       <c r="A16" s="103"/>
       <c r="B16" s="103" t="s">
-        <v>3170</v>
+        <v>3209</v>
       </c>
       <c r="C16" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D16" s="109" t="s">
-        <v>3171</v>
+        <v>3210</v>
       </c>
       <c r="E16" s="103" t="s">
-        <v>3172</v>
+        <v>3211</v>
       </c>
       <c r="F16" s="103" t="s">
         <v>146</v>
@@ -77002,16 +77314,16 @@
     <row r="17" spans="1:14" ht="45.6">
       <c r="A17" s="103"/>
       <c r="B17" s="103" t="s">
-        <v>3173</v>
+        <v>3212</v>
       </c>
       <c r="C17" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D17" s="103" t="s">
-        <v>3174</v>
+        <v>3213</v>
       </c>
       <c r="E17" s="103" t="s">
-        <v>3175</v>
+        <v>3214</v>
       </c>
       <c r="F17" s="103" t="s">
         <v>146</v>
@@ -77026,22 +77338,22 @@
       </c>
       <c r="K17" s="102"/>
       <c r="N17" s="107" t="s">
-        <v>3176</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="22.9">
       <c r="A18" s="103"/>
       <c r="B18" s="103" t="s">
-        <v>3177</v>
+        <v>3216</v>
       </c>
       <c r="C18" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D18" s="103" t="s">
-        <v>3178</v>
+        <v>3217</v>
       </c>
       <c r="E18" s="103" t="s">
-        <v>3179</v>
+        <v>3218</v>
       </c>
       <c r="F18" s="103" t="s">
         <v>146</v>
@@ -77056,22 +77368,22 @@
       </c>
       <c r="K18" s="102"/>
       <c r="N18" s="107" t="s">
-        <v>3180</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="34.15">
       <c r="A19" s="103"/>
       <c r="B19" s="103" t="s">
-        <v>3181</v>
+        <v>3220</v>
       </c>
       <c r="C19" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D19" s="103" t="s">
-        <v>3174</v>
+        <v>3213</v>
       </c>
       <c r="E19" s="103" t="s">
-        <v>3182</v>
+        <v>3221</v>
       </c>
       <c r="F19" s="103" t="s">
         <v>146</v>
@@ -77086,22 +77398,22 @@
       </c>
       <c r="K19" s="102"/>
       <c r="N19" s="107" t="s">
-        <v>3183</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="45.6">
       <c r="A20" s="103"/>
       <c r="B20" s="103" t="s">
-        <v>3184</v>
+        <v>3223</v>
       </c>
       <c r="C20" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D20" s="109" t="s">
-        <v>3185</v>
+        <v>3224</v>
       </c>
       <c r="E20" s="103" t="s">
-        <v>3186</v>
+        <v>3225</v>
       </c>
       <c r="F20" s="103" t="s">
         <v>146</v>
@@ -77116,22 +77428,22 @@
         <v>46272</v>
       </c>
       <c r="N20" s="107" t="s">
-        <v>3187</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="34.15">
       <c r="A21" s="103"/>
       <c r="B21" s="103" t="s">
-        <v>3188</v>
+        <v>3227</v>
       </c>
       <c r="C21" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D21" s="103" t="s">
-        <v>3158</v>
+        <v>3197</v>
       </c>
       <c r="E21" s="103" t="s">
-        <v>3189</v>
+        <v>3228</v>
       </c>
       <c r="F21" s="103" t="s">
         <v>146</v>
@@ -77146,22 +77458,22 @@
         <v>46353</v>
       </c>
       <c r="N21" s="107" t="s">
-        <v>3160</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="22.9">
       <c r="A22" s="103"/>
       <c r="B22" s="103" t="s">
-        <v>3190</v>
+        <v>3229</v>
       </c>
       <c r="C22" s="103" t="s">
         <v>1084</v>
       </c>
       <c r="D22" s="109" t="s">
-        <v>3158</v>
+        <v>3197</v>
       </c>
       <c r="E22" s="103" t="s">
-        <v>3162</v>
+        <v>3201</v>
       </c>
       <c r="F22" s="103" t="s">
         <v>146</v>
@@ -77176,7 +77488,7 @@
         <v>46353</v>
       </c>
       <c r="N22" s="107" t="s">
-        <v>3160</v>
+        <v>3199</v>
       </c>
     </row>
   </sheetData>
@@ -77308,7 +77620,7 @@
         <v>42</v>
       </c>
       <c r="AE1" s="22" t="s">
-        <v>3191</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="21" customFormat="1">
@@ -77383,7 +77695,7 @@
         <v>46598</v>
       </c>
       <c r="AE2" s="23" t="s">
-        <v>3192</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="3" spans="1:31" s="21" customFormat="1">
@@ -77998,7 +78310,7 @@
         <v>46265</v>
       </c>
       <c r="AE11" s="23" t="s">
-        <v>3193</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="12" spans="1:31" s="21" customFormat="1">
@@ -78408,7 +78720,7 @@
         <v>46295</v>
       </c>
       <c r="AE17" s="23" t="s">
-        <v>3194</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="18" spans="1:31" s="21" customFormat="1">
@@ -78830,7 +79142,7 @@
         <v>46385</v>
       </c>
       <c r="AE23" s="23" t="s">
-        <v>3195</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="24" spans="1:31" s="21" customFormat="1">
@@ -78907,7 +79219,7 @@
         <v>46295</v>
       </c>
       <c r="AE24" s="23" t="s">
-        <v>3196</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="25" spans="1:31" s="21" customFormat="1">
@@ -79321,7 +79633,7 @@
         <v>46325</v>
       </c>
       <c r="AE30" s="23" t="s">
-        <v>3197</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="31" spans="1:31" s="21" customFormat="1">
@@ -80197,7 +80509,7 @@
         <v>46171</v>
       </c>
       <c r="AE44" s="23" t="s">
-        <v>3198</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="45" spans="1:31" s="21" customFormat="1">
@@ -80278,14 +80590,14 @@
         <v>3098</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>3199</v>
+        <v>3238</v>
       </c>
       <c r="C46" s="23" t="s">
         <v>1092</v>
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23" t="s">
-        <v>3200</v>
+        <v>3239</v>
       </c>
       <c r="F46" s="23" t="s">
         <v>57</v>
@@ -80315,7 +80627,7 @@
       <c r="AC46" s="38"/>
       <c r="AD46" s="38"/>
       <c r="AE46" s="36" t="s">
-        <v>3201</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="47" spans="1:31" s="21" customFormat="1" ht="92.45">
@@ -80323,14 +80635,14 @@
         <v>3098</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>3202</v>
+        <v>3241</v>
       </c>
       <c r="C47" s="23" t="s">
         <v>1092</v>
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="23" t="s">
-        <v>3203</v>
+        <v>3242</v>
       </c>
       <c r="F47" s="23" t="s">
         <v>146</v>
@@ -80360,7 +80672,7 @@
       <c r="AC47" s="38"/>
       <c r="AD47" s="38"/>
       <c r="AE47" s="36" t="s">
-        <v>3204</v>
+        <v>3243</v>
       </c>
     </row>
   </sheetData>
@@ -81405,7 +81717,7 @@
         <v>3098</v>
       </c>
       <c r="B17" t="s">
-        <v>3205</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -81413,7 +81725,7 @@
         <v>3098</v>
       </c>
       <c r="B18" t="s">
-        <v>3206</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -81421,7 +81733,7 @@
         <v>3098</v>
       </c>
       <c r="B19" t="s">
-        <v>3207</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -81429,7 +81741,7 @@
         <v>3098</v>
       </c>
       <c r="B20" t="s">
-        <v>3208</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -81437,7 +81749,7 @@
         <v>3098</v>
       </c>
       <c r="B21" t="s">
-        <v>3209</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -81445,7 +81757,7 @@
         <v>3098</v>
       </c>
       <c r="B22" t="s">
-        <v>3210</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -81453,7 +81765,7 @@
         <v>3098</v>
       </c>
       <c r="B23" t="s">
-        <v>3211</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -81461,7 +81773,7 @@
         <v>3098</v>
       </c>
       <c r="B24" t="s">
-        <v>3212</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -81469,7 +81781,7 @@
         <v>3098</v>
       </c>
       <c r="B25" t="s">
-        <v>3213</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -81477,7 +81789,7 @@
         <v>3098</v>
       </c>
       <c r="B26" t="s">
-        <v>3214</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -81485,7 +81797,7 @@
         <v>3098</v>
       </c>
       <c r="B27" t="s">
-        <v>3215</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -81493,7 +81805,7 @@
         <v>3098</v>
       </c>
       <c r="B28" t="s">
-        <v>3216</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -81501,7 +81813,7 @@
         <v>3098</v>
       </c>
       <c r="B29" t="s">
-        <v>3217</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -81509,7 +81821,7 @@
         <v>3098</v>
       </c>
       <c r="B30" t="s">
-        <v>3218</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -81517,7 +81829,7 @@
         <v>3098</v>
       </c>
       <c r="B31" t="s">
-        <v>3219</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -81525,7 +81837,7 @@
         <v>3098</v>
       </c>
       <c r="B32" t="s">
-        <v>3220</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -81533,7 +81845,7 @@
         <v>3098</v>
       </c>
       <c r="B33" t="s">
-        <v>3221</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -81541,7 +81853,7 @@
         <v>3098</v>
       </c>
       <c r="B34" t="s">
-        <v>3222</v>
+        <v>3261</v>
       </c>
     </row>
   </sheetData>
